--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$83</f>
+              <f>'Equity-Kurve'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$83</f>
+              <f>'Equity-Kurve'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11 23:50 UTC</t>
+          <t>2026-09-15 00:12 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5154.88 CHF</t>
+          <t>5085.24 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3.10 %</t>
+          <t>+1.70 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+9.83 %</t>
+          <t>+5.27 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1711,6 +1711,16 @@
       </c>
       <c r="B83" t="n">
         <v>5154.88</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>5085.24</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$84</f>
+              <f>'Equity-Kurve'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$84</f>
+              <f>'Equity-Kurve'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:12 UTC</t>
+          <t>2026-09-15 23:55 UTC</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5085.24 CHF</t>
+          <t>5046.94 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+1.70 %</t>
+          <t>+0.94 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+5.27 %</t>
+          <t>+2.84 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1721,6 +1721,16 @@
       </c>
       <c r="B84" t="n">
         <v>5085.24</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>5046.94</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$85</f>
+              <f>'Equity-Kurve'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$85</f>
+              <f>'Equity-Kurve'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 23:55 UTC</t>
+          <t>2026-09-17 00:01 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5046.94 CHF</t>
+          <t>4936.23 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.94 %</t>
+          <t>-1.28 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+2.84 %</t>
+          <t>-3.73 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1731,6 +1731,16 @@
       </c>
       <c r="B85" t="n">
         <v>5046.94</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4936.23</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$86</f>
+              <f>'Equity-Kurve'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$86</f>
+              <f>'Equity-Kurve'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 00:01 UTC</t>
+          <t>2026-09-17 23:52 UTC</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4936.23 CHF</t>
+          <t>4945.11 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.28 %</t>
+          <t>-1.10 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.73 %</t>
+          <t>-3.18 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B86"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1741,6 +1741,16 @@
       </c>
       <c r="B86" t="n">
         <v>4936.23</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>4945.11</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$87</f>
+              <f>'Equity-Kurve'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$87</f>
+              <f>'Equity-Kurve'!$B$2:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 23:52 UTC</t>
+          <t>2026-09-18 23:50 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4945.11 CHF</t>
+          <t>4956.28 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.10 %</t>
+          <t>-0.87 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.18 %</t>
+          <t>-2.51 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1751,6 +1751,16 @@
       </c>
       <c r="B87" t="n">
         <v>4945.11</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>4956.28</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$88</f>
+              <f>'Equity-Kurve'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$88</f>
+              <f>'Equity-Kurve'!$B$2:$B$89</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18 23:50 UTC</t>
+          <t>2026-09-22 00:32 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4956.28 CHF</t>
+          <t>4940.54 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.87 %</t>
+          <t>-1.19 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-2.51 %</t>
+          <t>-3.37 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,16 @@
       </c>
       <c r="B88" t="n">
         <v>4956.28</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>4940.54</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$89</f>
+              <f>'Equity-Kurve'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$89</f>
+              <f>'Equity-Kurve'!$B$2:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22 00:32 UTC</t>
+          <t>2026-09-22 23:58 UTC</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4940.54 CHF</t>
+          <t>4917.94 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.19 %</t>
+          <t>-1.64 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.37 %</t>
+          <t>-4.58 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1771,6 +1771,16 @@
       </c>
       <c r="B89" t="n">
         <v>4940.54</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4917.94</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$90</f>
+              <f>'Equity-Kurve'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$90</f>
+              <f>'Equity-Kurve'!$B$2:$B$91</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22 23:58 UTC</t>
+          <t>2026-09-24 00:11 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4917.94 CHF</t>
+          <t>4811.16 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.64 %</t>
+          <t>-3.78 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-4.58 %</t>
+          <t>-10.22 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-7.18 %</t>
+          <t>-8.00 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1781,6 +1781,16 @@
       </c>
       <c r="B90" t="n">
         <v>4917.94</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4811.16</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$91</f>
+              <f>'Equity-Kurve'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$91</f>
+              <f>'Equity-Kurve'!$B$2:$B$92</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24 00:11 UTC</t>
+          <t>2026-09-25 00:13 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4811.16 CHF</t>
+          <t>4743.46 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.78 %</t>
+          <t>-5.13 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-10.22 %</t>
+          <t>-13.57 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-8.00 %</t>
+          <t>-9.29 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1791,6 +1791,16 @@
       </c>
       <c r="B91" t="n">
         <v>4811.16</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>4743.46</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$92</f>
+              <f>'Equity-Kurve'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$92</f>
+              <f>'Equity-Kurve'!$B$2:$B$93</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 00:13 UTC</t>
+          <t>2026-09-26 00:20 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4743.46 CHF</t>
+          <t>4800.55 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.13 %</t>
+          <t>-3.99 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-13.57 %</t>
+          <t>-10.55 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1801,6 +1801,16 @@
       </c>
       <c r="B92" t="n">
         <v>4743.46</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4800.55</v>
       </c>
     </row>
   </sheetData>
